--- a/DataRepo/data/tests/submission_v3/study.xlsx
+++ b/DataRepo/data/tests/submission_v3/study.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/submission_v3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DCADA0-A873-B34A-812C-ACC89559BB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA311036-2EE3-2140-9720-E9BF5B0B77EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="500" windowWidth="37040" windowHeight="26740" tabRatio="500" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="500" windowWidth="37040" windowHeight="26740" tabRatio="500" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="5" r:id="rId1"/>
@@ -21,13 +21,13 @@
     <sheet name="Infusates" sheetId="6" r:id="rId6"/>
     <sheet name="Tracers" sheetId="7" r:id="rId7"/>
     <sheet name="Compounds" sheetId="8" r:id="rId8"/>
-    <sheet name="Peak Annotation Files" sheetId="12" r:id="rId9"/>
-    <sheet name="Peak Annotation Details" sheetId="9" r:id="rId10"/>
-    <sheet name="Sequences" sheetId="10" r:id="rId11"/>
-    <sheet name="LC Protocols" sheetId="13" r:id="rId12"/>
+    <sheet name="LC Protocols" sheetId="13" r:id="rId9"/>
+    <sheet name="Sequences" sheetId="10" r:id="rId10"/>
+    <sheet name="Peak Annotation Files" sheetId="12" r:id="rId11"/>
+    <sheet name="Peak Annotation Details" sheetId="9" r:id="rId12"/>
     <sheet name="Defaults" sheetId="11" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="534">
   <si>
     <t>Animal ID</t>
   </si>
@@ -1565,9 +1565,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Sample Name Prefix</t>
-  </si>
-  <si>
     <t>BCAAs (VLI) {valine-[13C5,15N1]; leucine-[13C6,15N1]; isoleucine-[13C6,15N1]}</t>
   </si>
   <si>
@@ -1644,6 +1641,15 @@
   </si>
   <si>
     <t>alanine-[13C3,15N1][180]</t>
+  </si>
+  <si>
+    <t>Peak Annotation File</t>
+  </si>
+  <si>
+    <t>File Format</t>
+  </si>
+  <si>
+    <t>Default Sequence Name</t>
   </si>
 </sst>
 </file>
@@ -2221,6 +2227,167 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20C6601-13DF-A246-A06D-0D094CDDF538}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="43.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A1" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E2" s="7">
+        <v>44355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E3" s="7">
+        <v>44488</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E4" s="7">
+        <v>44034</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8236A626-A31D-6D4A-BDF3-4C2E37787CF8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CC3F7EA2-A21F-974C-966F-6B514DCC32CF}">
+          <x14:formula1>
+            <xm:f>Sequences!$A$2:$A$10000</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E47295-2681-5A40-8A8D-DC3FAC0C389C}">
   <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -2246,7 +2413,7 @@
         <v>334</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>501</v>
@@ -2267,7 +2434,7 @@
         <v>494</v>
       </c>
       <c r="E2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2284,7 +2451,7 @@
         <v>494</v>
       </c>
       <c r="E3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2301,7 +2468,7 @@
         <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2318,7 +2485,7 @@
         <v>494</v>
       </c>
       <c r="E5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2335,7 +2502,7 @@
         <v>494</v>
       </c>
       <c r="E6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2352,7 +2519,7 @@
         <v>494</v>
       </c>
       <c r="E7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2369,7 +2536,7 @@
         <v>494</v>
       </c>
       <c r="E8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2386,7 +2553,7 @@
         <v>494</v>
       </c>
       <c r="E9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2403,7 +2570,7 @@
         <v>494</v>
       </c>
       <c r="E10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2420,7 +2587,7 @@
         <v>494</v>
       </c>
       <c r="E11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2437,7 +2604,7 @@
         <v>494</v>
       </c>
       <c r="E12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2454,7 +2621,7 @@
         <v>494</v>
       </c>
       <c r="E13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2471,7 +2638,7 @@
         <v>494</v>
       </c>
       <c r="E14" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2488,7 +2655,7 @@
         <v>494</v>
       </c>
       <c r="E15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -2505,7 +2672,7 @@
         <v>494</v>
       </c>
       <c r="E16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2522,7 +2689,7 @@
         <v>494</v>
       </c>
       <c r="E17" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2539,7 +2706,7 @@
         <v>494</v>
       </c>
       <c r="E18" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2556,7 +2723,7 @@
         <v>494</v>
       </c>
       <c r="E19" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2573,7 +2740,7 @@
         <v>494</v>
       </c>
       <c r="E20" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2590,7 +2757,7 @@
         <v>494</v>
       </c>
       <c r="E21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2607,7 +2774,7 @@
         <v>494</v>
       </c>
       <c r="E22" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2624,7 +2791,7 @@
         <v>494</v>
       </c>
       <c r="E23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2641,7 +2808,7 @@
         <v>494</v>
       </c>
       <c r="E24" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2658,7 +2825,7 @@
         <v>494</v>
       </c>
       <c r="E25" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2675,7 +2842,7 @@
         <v>494</v>
       </c>
       <c r="E26" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2692,7 +2859,7 @@
         <v>494</v>
       </c>
       <c r="E27" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2709,7 +2876,7 @@
         <v>494</v>
       </c>
       <c r="E28" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2726,7 +2893,7 @@
         <v>494</v>
       </c>
       <c r="E29" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2743,7 +2910,7 @@
         <v>494</v>
       </c>
       <c r="E30" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2760,7 +2927,7 @@
         <v>494</v>
       </c>
       <c r="E31" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2777,7 +2944,7 @@
         <v>494</v>
       </c>
       <c r="E32" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2794,7 +2961,7 @@
         <v>494</v>
       </c>
       <c r="E33" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2811,7 +2978,7 @@
         <v>494</v>
       </c>
       <c r="E34" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2828,7 +2995,7 @@
         <v>494</v>
       </c>
       <c r="E35" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2845,7 +3012,7 @@
         <v>494</v>
       </c>
       <c r="E36" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2862,7 +3029,7 @@
         <v>494</v>
       </c>
       <c r="E37" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2879,7 +3046,7 @@
         <v>495</v>
       </c>
       <c r="E38" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2896,7 +3063,7 @@
         <v>495</v>
       </c>
       <c r="E39" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2913,7 +3080,7 @@
         <v>495</v>
       </c>
       <c r="E40" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2930,7 +3097,7 @@
         <v>495</v>
       </c>
       <c r="E41" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2947,7 +3114,7 @@
         <v>495</v>
       </c>
       <c r="E42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2964,7 +3131,7 @@
         <v>495</v>
       </c>
       <c r="E43" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2981,7 +3148,7 @@
         <v>495</v>
       </c>
       <c r="E44" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -2998,7 +3165,7 @@
         <v>495</v>
       </c>
       <c r="E45" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3015,7 +3182,7 @@
         <v>495</v>
       </c>
       <c r="E46" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3032,7 +3199,7 @@
         <v>495</v>
       </c>
       <c r="E47" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3049,7 +3216,7 @@
         <v>495</v>
       </c>
       <c r="E48" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3066,7 +3233,7 @@
         <v>495</v>
       </c>
       <c r="E49" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3083,7 +3250,7 @@
         <v>495</v>
       </c>
       <c r="E50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3100,7 +3267,7 @@
         <v>495</v>
       </c>
       <c r="E51" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3117,7 +3284,7 @@
         <v>495</v>
       </c>
       <c r="E52" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3134,7 +3301,7 @@
         <v>495</v>
       </c>
       <c r="E53" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3151,7 +3318,7 @@
         <v>495</v>
       </c>
       <c r="E54" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3168,7 +3335,7 @@
         <v>495</v>
       </c>
       <c r="E55" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3185,7 +3352,7 @@
         <v>495</v>
       </c>
       <c r="E56" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3202,7 +3369,7 @@
         <v>495</v>
       </c>
       <c r="E57" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3219,7 +3386,7 @@
         <v>495</v>
       </c>
       <c r="E58" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3236,7 +3403,7 @@
         <v>495</v>
       </c>
       <c r="E59" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3253,7 +3420,7 @@
         <v>495</v>
       </c>
       <c r="E60" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3270,7 +3437,7 @@
         <v>495</v>
       </c>
       <c r="E61" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3287,7 +3454,7 @@
         <v>495</v>
       </c>
       <c r="E62" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3304,7 +3471,7 @@
         <v>495</v>
       </c>
       <c r="E63" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3321,7 +3488,7 @@
         <v>495</v>
       </c>
       <c r="E64" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3338,7 +3505,7 @@
         <v>495</v>
       </c>
       <c r="E65" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3355,7 +3522,7 @@
         <v>495</v>
       </c>
       <c r="E66" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3372,7 +3539,7 @@
         <v>495</v>
       </c>
       <c r="E67" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3389,7 +3556,7 @@
         <v>495</v>
       </c>
       <c r="E68" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3406,7 +3573,7 @@
         <v>495</v>
       </c>
       <c r="E69" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3423,7 +3590,7 @@
         <v>495</v>
       </c>
       <c r="E70" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3440,7 +3607,7 @@
         <v>495</v>
       </c>
       <c r="E71" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3457,7 +3624,7 @@
         <v>495</v>
       </c>
       <c r="E72" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3474,7 +3641,7 @@
         <v>495</v>
       </c>
       <c r="E73" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3491,7 +3658,7 @@
         <v>493</v>
       </c>
       <c r="E74" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3508,7 +3675,7 @@
         <v>493</v>
       </c>
       <c r="E75" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3525,7 +3692,7 @@
         <v>493</v>
       </c>
       <c r="E76" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3542,7 +3709,7 @@
         <v>493</v>
       </c>
       <c r="E77" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3559,7 +3726,7 @@
         <v>493</v>
       </c>
       <c r="E78" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3576,7 +3743,7 @@
         <v>493</v>
       </c>
       <c r="E79" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3593,7 +3760,7 @@
         <v>493</v>
       </c>
       <c r="E80" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3610,7 +3777,7 @@
         <v>493</v>
       </c>
       <c r="E81" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3627,7 +3794,7 @@
         <v>493</v>
       </c>
       <c r="E82" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3644,7 +3811,7 @@
         <v>493</v>
       </c>
       <c r="E83" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3661,7 +3828,7 @@
         <v>493</v>
       </c>
       <c r="E84" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3678,7 +3845,7 @@
         <v>493</v>
       </c>
       <c r="E85" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3695,7 +3862,7 @@
         <v>493</v>
       </c>
       <c r="E86" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3712,7 +3879,7 @@
         <v>493</v>
       </c>
       <c r="E87" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3729,7 +3896,7 @@
         <v>493</v>
       </c>
       <c r="E88" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3746,7 +3913,7 @@
         <v>493</v>
       </c>
       <c r="E89" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3763,7 +3930,7 @@
         <v>493</v>
       </c>
       <c r="E90" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3780,7 +3947,7 @@
         <v>493</v>
       </c>
       <c r="E91" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3797,7 +3964,7 @@
         <v>493</v>
       </c>
       <c r="E92" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3814,7 +3981,7 @@
         <v>493</v>
       </c>
       <c r="E93" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3831,7 +3998,7 @@
         <v>493</v>
       </c>
       <c r="E94" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3848,7 +4015,7 @@
         <v>493</v>
       </c>
       <c r="E95" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3865,7 +4032,7 @@
         <v>493</v>
       </c>
       <c r="E96" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3882,7 +4049,7 @@
         <v>493</v>
       </c>
       <c r="E97" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3899,7 +4066,7 @@
         <v>493</v>
       </c>
       <c r="E98" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3916,7 +4083,7 @@
         <v>493</v>
       </c>
       <c r="E99" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3933,7 +4100,7 @@
         <v>493</v>
       </c>
       <c r="E100" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3950,7 +4117,7 @@
         <v>493</v>
       </c>
       <c r="E101" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3967,7 +4134,7 @@
         <v>493</v>
       </c>
       <c r="E102" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3984,7 +4151,7 @@
         <v>493</v>
       </c>
       <c r="E103" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4001,7 +4168,7 @@
         <v>493</v>
       </c>
       <c r="E104" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4018,7 +4185,7 @@
         <v>493</v>
       </c>
       <c r="E105" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4035,7 +4202,7 @@
         <v>493</v>
       </c>
       <c r="E106" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4052,7 +4219,7 @@
         <v>493</v>
       </c>
       <c r="E107" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4069,7 +4236,7 @@
         <v>493</v>
       </c>
       <c r="E108" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4086,7 +4253,7 @@
         <v>493</v>
       </c>
       <c r="E109" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4103,7 +4270,7 @@
         <v>493</v>
       </c>
       <c r="E110" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4120,7 +4287,7 @@
         <v>493</v>
       </c>
       <c r="E111" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4137,7 +4304,7 @@
         <v>493</v>
       </c>
       <c r="E112" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4154,7 +4321,7 @@
         <v>493</v>
       </c>
       <c r="E113" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4171,7 +4338,7 @@
         <v>493</v>
       </c>
       <c r="E114" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4188,7 +4355,7 @@
         <v>493</v>
       </c>
       <c r="E115" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4205,7 +4372,7 @@
         <v>493</v>
       </c>
       <c r="E116" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4222,7 +4389,7 @@
         <v>493</v>
       </c>
       <c r="E117" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4239,7 +4406,7 @@
         <v>493</v>
       </c>
       <c r="E118" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4256,7 +4423,7 @@
         <v>493</v>
       </c>
       <c r="E119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4273,7 +4440,7 @@
         <v>493</v>
       </c>
       <c r="E120" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4290,7 +4457,7 @@
         <v>493</v>
       </c>
       <c r="E121" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4307,7 +4474,7 @@
         <v>493</v>
       </c>
       <c r="E122" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4324,7 +4491,7 @@
         <v>493</v>
       </c>
       <c r="E123" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4341,7 +4508,7 @@
         <v>493</v>
       </c>
       <c r="E124" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4358,7 +4525,7 @@
         <v>493</v>
       </c>
       <c r="E125" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4375,7 +4542,7 @@
         <v>493</v>
       </c>
       <c r="E126" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4392,7 +4559,7 @@
         <v>493</v>
       </c>
       <c r="E127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4409,7 +4576,7 @@
         <v>493</v>
       </c>
       <c r="E128" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4426,7 +4593,7 @@
         <v>493</v>
       </c>
       <c r="E129" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4443,7 +4610,7 @@
         <v>493</v>
       </c>
       <c r="E130" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4460,7 +4627,7 @@
         <v>493</v>
       </c>
       <c r="E131" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4477,7 +4644,7 @@
         <v>493</v>
       </c>
       <c r="E132" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4494,7 +4661,7 @@
         <v>493</v>
       </c>
       <c r="E133" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4511,7 +4678,7 @@
         <v>493</v>
       </c>
       <c r="E134" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4528,7 +4695,7 @@
         <v>493</v>
       </c>
       <c r="E135" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4545,7 +4712,7 @@
         <v>493</v>
       </c>
       <c r="E136" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4562,7 +4729,7 @@
         <v>493</v>
       </c>
       <c r="E137" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4579,7 +4746,7 @@
         <v>493</v>
       </c>
       <c r="E138" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4596,7 +4763,7 @@
         <v>493</v>
       </c>
       <c r="E139" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4613,7 +4780,7 @@
         <v>493</v>
       </c>
       <c r="E140" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4630,7 +4797,7 @@
         <v>493</v>
       </c>
       <c r="E141" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4647,7 +4814,7 @@
         <v>493</v>
       </c>
       <c r="E142" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4664,7 +4831,7 @@
         <v>493</v>
       </c>
       <c r="E143" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4681,7 +4848,7 @@
         <v>493</v>
       </c>
       <c r="E144" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4698,7 +4865,7 @@
         <v>493</v>
       </c>
       <c r="E145" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4715,7 +4882,7 @@
         <v>493</v>
       </c>
       <c r="E146" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4732,7 +4899,7 @@
         <v>493</v>
       </c>
       <c r="E147" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4749,7 +4916,7 @@
         <v>493</v>
       </c>
       <c r="E148" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4766,7 +4933,7 @@
         <v>493</v>
       </c>
       <c r="E149" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4783,7 +4950,7 @@
         <v>493</v>
       </c>
       <c r="E150" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4800,7 +4967,7 @@
         <v>493</v>
       </c>
       <c r="E151" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4817,7 +4984,7 @@
         <v>493</v>
       </c>
       <c r="E152" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4834,7 +5001,7 @@
         <v>493</v>
       </c>
       <c r="E153" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4851,7 +5018,7 @@
         <v>493</v>
       </c>
       <c r="E154" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4868,7 +5035,7 @@
         <v>493</v>
       </c>
       <c r="E155" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4885,7 +5052,7 @@
         <v>493</v>
       </c>
       <c r="E156" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -4902,7 +5069,7 @@
         <v>493</v>
       </c>
       <c r="E157" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -4922,149 +5089,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20C6601-13DF-A246-A06D-0D094CDDF538}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="43.5" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
-        <v>524</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
-        <v>526</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="E2" s="7">
-        <v>44355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
-        <v>527</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="E3" s="7">
-        <v>44488</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
-        <v>528</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="E4" s="7">
-        <v>44034</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC6B7B7-1799-7447-8892-685572B624F5}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
-        <v>504</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14" x14ac:dyDescent="0.15">
-      <c r="A2" s="21" t="s">
-        <v>521</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="C2" s="15">
-        <v>25</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="20"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="20"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E98A77-02BD-684D-92F1-1DDAA652A830}">
   <dimension ref="A1:C7"/>
@@ -5077,18 +5101,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="18" t="s">
         <v>516</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>332</v>
@@ -5099,7 +5123,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="19" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>333</v>
@@ -5110,7 +5134,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="19" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>500</v>
@@ -5121,7 +5145,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>331</v>
@@ -5132,18 +5156,18 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>330</v>
@@ -5225,7 +5249,7 @@
         <v>26.4</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G2" s="4">
         <v>0.1</v>
@@ -5260,7 +5284,7 @@
         <v>27.5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G3" s="4">
         <v>0.1</v>
@@ -5295,7 +5319,7 @@
         <v>27.1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G4" s="4">
         <v>0.1</v>
@@ -5330,7 +5354,7 @@
         <v>42.6</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G5" s="4">
         <v>7.0999999999999994E-2</v>
@@ -5365,7 +5389,7 @@
         <v>44.1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G6" s="4">
         <v>6.8000000000000005E-2</v>
@@ -5400,7 +5424,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G7" s="4">
         <v>6.5000000000000002E-2</v>
@@ -5435,7 +5459,7 @@
         <v>27.5</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G8" s="4">
         <v>0.1</v>
@@ -5470,7 +5494,7 @@
         <v>27.5</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G9" s="4">
         <v>0.1</v>
@@ -5505,7 +5529,7 @@
         <v>28.4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G10" s="4">
         <v>0.106</v>
@@ -5540,7 +5564,7 @@
         <v>28.7</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G11" s="4">
         <v>0.105</v>
@@ -5575,7 +5599,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G12" s="4">
         <v>0.06</v>
@@ -5610,7 +5634,7 @@
         <v>54.3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G13" s="4">
         <v>5.5E-2</v>
@@ -21882,7 +21906,7 @@
         <v>261</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>262</v>
@@ -21930,13 +21954,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E4">
         <v>20</v>
@@ -21947,13 +21971,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E5">
         <v>24</v>
@@ -21964,13 +21988,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -22015,7 +22039,7 @@
         <v>268</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -22106,7 +22130,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>271</v>
@@ -22118,7 +22142,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
@@ -22126,7 +22150,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>272</v>
@@ -22138,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.15">
@@ -22146,7 +22170,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>271</v>
@@ -22158,7 +22182,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
@@ -22166,7 +22190,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>272</v>
@@ -22178,7 +22202,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
@@ -22186,7 +22210,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>271</v>
@@ -22198,7 +22222,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.15">
@@ -22206,7 +22230,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>272</v>
@@ -22218,7 +22242,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="4:4" ht="15" x14ac:dyDescent="0.2">
@@ -22464,49 +22488,53 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8236A626-A31D-6D4A-BDF3-4C2E37787CF8}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC6B7B7-1799-7447-8892-685572B624F5}">
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>334</v>
+    <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.15">
+      <c r="A1" s="23" t="s">
+        <v>504</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>494</v>
+        <v>528</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14" x14ac:dyDescent="0.15">
+      <c r="A2" s="21" t="s">
+        <v>520</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>495</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>493</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>496</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="C2" s="15">
+        <v>25</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="20"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
